--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104636_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104636_W20.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4933</v>
+        <v>6.7281</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8252</v>
+        <v>1.2635</v>
       </c>
       <c r="F2" t="n">
-        <v>2.668</v>
+        <v>5.4646</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9613</v>
+        <v>-0.5284</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2123</v>
+        <v>-1.5364</v>
       </c>
       <c r="I2" t="n">
-        <v>0.749</v>
+        <v>1.008</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3804</v>
+        <v>-2.3529</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6714</v>
+        <v>-2.2105</v>
       </c>
       <c r="L2" t="n">
-        <v>0.709</v>
+        <v>-0.1424</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5809</v>
+        <v>1.8245</v>
       </c>
       <c r="N2" t="n">
-        <v>1.5409</v>
+        <v>0.6741</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04</v>
+        <v>1.1504</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>4.9026</v>
+        <v>0.6192</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4449</v>
+        <v>0.348</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4577</v>
+        <v>0.2711</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.1853</v>
+        <v>4.8163</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1853</v>
+        <v>1.5479</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1234</v>
+        <v>5.8987</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5993000000000001</v>
+        <v>2.522</v>
       </c>
       <c r="F3" t="n">
-        <v>5.5241</v>
+        <v>3.3767</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5157</v>
+        <v>1.93</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5338</v>
+        <v>2.292</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0181</v>
+        <v>-0.3621</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.3158</v>
+        <v>0.8938</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.193</v>
+        <v>1.2443</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1228</v>
+        <v>-0.3505</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8001</v>
+        <v>1.0361</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6592</v>
+        <v>1.0477</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1409</v>
+        <v>-0.0116</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0039</v>
+        <v>0.8792</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3629</v>
+        <v>0.5874</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3668</v>
+        <v>0.2919</v>
       </c>
       <c r="V3" t="n">
-        <v>4.8205</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>3.278</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>1.5425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9452</v>
+        <v>5.1473</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1211</v>
+        <v>2.2979</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8241</v>
+        <v>2.8494</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4761</v>
+        <v>2.4178</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2093</v>
+        <v>1.433</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6854</v>
+        <v>0.9848</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1796</v>
+        <v>0.9091</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3649</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>4.5445</v>
+        <v>-0.0077</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2965</v>
+        <v>1.5087</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1556</v>
+        <v>0.5162</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1409</v>
+        <v>0.9925</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1496</v>
+        <v>0.2742</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2098</v>
+        <v>0.2993</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0602</v>
+        <v>-0.0251</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6083</v>
+        <v>4.9861</v>
       </c>
       <c r="E5" t="n">
-        <v>1.725</v>
+        <v>1.8509</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8833</v>
+        <v>3.1352</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9345</v>
+        <v>4.4693</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2943</v>
+        <v>-1.201</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3599</v>
+        <v>5.6703</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9157999999999999</v>
+        <v>3.1474</v>
       </c>
       <c r="K5" t="n">
-        <v>1.257</v>
+        <v>-1.3724</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3413</v>
+        <v>4.5199</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0187</v>
+        <v>1.3219</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0373</v>
+        <v>0.1715</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0186</v>
+        <v>1.1504</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4189</v>
+        <v>1.1997</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2419</v>
+        <v>0.9797</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1769</v>
+        <v>0.22</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.3607</v>
+        <v>4.7527</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7246</v>
+        <v>2.6833</v>
       </c>
       <c r="F6" t="n">
-        <v>2.636</v>
+        <v>2.0695</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4109</v>
+        <v>2.9503</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4299</v>
+        <v>2.1979</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9809</v>
+        <v>0.7524</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9253</v>
+        <v>1.355</v>
       </c>
       <c r="K6" t="n">
-        <v>0.928</v>
+        <v>0.6475</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0027</v>
+        <v>0.7075</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4856</v>
+        <v>1.5953</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5019</v>
+        <v>1.5504</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9837</v>
+        <v>0.0449</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5039</v>
+        <v>2.1603</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2934</v>
+        <v>1.3283</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2105</v>
+        <v>0.832</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>-2.1789</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.8395</v>
+        <v>4.4455</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0588</v>
+        <v>-0.8036</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8983</v>
+        <v>5.2491</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0163</v>
+        <v>2.0098</v>
       </c>
       <c r="H7" t="n">
-        <v>4.0101</v>
+        <v>4.0013</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.9938</v>
+        <v>-1.9915</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5493</v>
+        <v>0.5127</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7218</v>
+        <v>2.6955</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.1725</v>
+        <v>-2.1827</v>
       </c>
       <c r="M7" t="n">
-        <v>1.467</v>
+        <v>1.4971</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2883</v>
+        <v>1.3058</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8232</v>
+        <v>1.4357</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8861</v>
+        <v>0.4153</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7094</v>
+        <v>1.0204</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.5949</v>
+        <v>2.5757</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7286</v>
+        <v>-0.4234</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8663</v>
+        <v>2.9991</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2441</v>
+        <v>0.8253</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7563</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4878</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9263</v>
+        <v>-0.5555</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8516</v>
+        <v>-1.6277</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0746</v>
+        <v>1.0722</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3178</v>
+        <v>1.3809</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0954</v>
+        <v>1.5504</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4132</v>
+        <v>-0.1695</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.722</v>
+        <v>2.2763</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>2.2763</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9802</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1122</v>
+        <v>0.1321</v>
       </c>
       <c r="U8" t="n">
-        <v>0.868</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>-1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1926</v>
+        <v>1.8306</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3574</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8353</v>
+        <v>1.7354</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0406</v>
+        <v>2.0375</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2077</v>
+        <v>4.2049</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1671</v>
+        <v>-2.1674</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3792</v>
+        <v>1.3593</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8399</v>
+        <v>2.8268</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6614</v>
+        <v>0.6782</v>
       </c>
       <c r="N9" t="n">
-        <v>1.3678</v>
+        <v>1.378</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7645</v>
+        <v>1.4077</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0858</v>
+        <v>0.8545</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6787</v>
+        <v>0.5532</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3941</v>
+        <v>1.5015</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2306</v>
+        <v>-0.0674</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6247</v>
+        <v>1.569</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8300999999999999</v>
+        <v>1.239</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0735</v>
+        <v>0.7472</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9036</v>
+        <v>0.4917</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.535</v>
+        <v>0.9083</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6145</v>
+        <v>0.8339</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0795</v>
+        <v>0.0745</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3651</v>
+        <v>0.3306</v>
       </c>
       <c r="N10" t="n">
-        <v>1.5409</v>
+        <v>-0.0866</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1759</v>
+        <v>0.4173</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2683</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4509</v>
+        <v>1.9046</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6956</v>
+        <v>1.3492</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2447</v>
+        <v>0.5554</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8899</v>
+        <v>0.8454</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.3763</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2726</v>
+        <v>0.4691</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2516</v>
+        <v>1.2566</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2121</v>
+        <v>0.2152</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0396</v>
+        <v>1.0413</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2434</v>
+        <v>1.2405</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1568</v>
+        <v>1.1543</v>
       </c>
       <c r="M11" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3188</v>
+        <v>0.2717</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5081</v>
+        <v>0.2739</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1893</v>
+        <v>-0.0022</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6851</v>
+        <v>-2.346</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4675</v>
+        <v>-1.1801</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2176</v>
+        <v>-1.1659</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6196</v>
+        <v>-0.6157</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5397</v>
+        <v>-0.5399</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0799</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6278</v>
+        <v>-0.6317</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6651</v>
+        <v>-0.669</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M12" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3486</v>
+        <v>0.6747</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2945</v>
+        <v>0.5898</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0541</v>
+        <v>0.0849</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2009</v>
+        <v>-2.8169</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7654</v>
+        <v>-2.7581</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4355</v>
+        <v>-0.0588</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8344</v>
+        <v>2.8185</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5008</v>
+        <v>3.4874</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6664</v>
+        <v>-0.669</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6952</v>
+        <v>1.6546</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3452</v>
+        <v>3.316</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.6501</v>
+        <v>-1.6614</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1392</v>
+        <v>1.1639</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0619</v>
+        <v>0.345</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5383</v>
+        <v>0.5269</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5235</v>
+        <v>-0.1819</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.571</v>
+        <v>-2.5659</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>33.5559</v>
+        <v>33.5487</v>
       </c>
       <c r="E14" t="n">
-        <v>6.176299999999999</v>
+        <v>5.8565</v>
       </c>
       <c r="F14" t="n">
-        <v>27.3796</v>
+        <v>27.6924</v>
       </c>
       <c r="G14" t="n">
-        <v>20.8646</v>
+        <v>20.81</v>
       </c>
       <c r="H14" t="n">
-        <v>15.2672</v>
+        <v>15.2243</v>
       </c>
       <c r="I14" t="n">
-        <v>5.597299999999999</v>
+        <v>5.5854</v>
       </c>
       <c r="J14" t="n">
-        <v>8.715900000000001</v>
+        <v>8.4406</v>
       </c>
       <c r="K14" t="n">
-        <v>6.864000000000001</v>
+        <v>6.687399999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8515</v>
+        <v>1.7533</v>
       </c>
       <c r="M14" t="n">
-        <v>12.1487</v>
+        <v>12.3692</v>
       </c>
       <c r="N14" t="n">
-        <v>8.4031</v>
+        <v>8.536999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>3.745900000000001</v>
+        <v>3.8323</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.1467</v>
+        <v>-18.2106</v>
       </c>
       <c r="R14" t="n">
-        <v>18.1467</v>
+        <v>18.2107</v>
       </c>
       <c r="S14" t="n">
-        <v>11.8558</v>
+        <v>11.8933</v>
       </c>
       <c r="T14" t="n">
-        <v>7.6371</v>
+        <v>7.6844</v>
       </c>
       <c r="U14" t="n">
-        <v>4.218999999999999</v>
+        <v>4.2089</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8354000000000004</v>
+        <v>0.8454999999999995</v>
       </c>
       <c r="W14" t="n">
-        <v>7.9701</v>
+        <v>7.941799999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.1346</v>
+        <v>-7.096299999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3253</v>
+        <v>1.7028</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1451</v>
+        <v>0.5208</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1802</v>
+        <v>1.182</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2746</v>
+        <v>0.413</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3781</v>
+        <v>-0.2995</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1035</v>
+        <v>0.7125</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1321</v>
+        <v>1.028</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.6837</v>
+        <v>0.8791</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5516</v>
+        <v>0.1489</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1425</v>
+        <v>-0.615</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6944</v>
+        <v>-1.1786</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4823</v>
+        <v>-1.0744</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5455</v>
+        <v>-0.8228</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.2516</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.3155</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5617</v>
+        <v>0.607</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1765</v>
+        <v>-1.4219</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7382</v>
+        <v>2.0288</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3863</v>
+        <v>-1.2735</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3148</v>
+        <v>-2.3726</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7010999999999999</v>
+        <v>1.0991</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0324</v>
+        <v>-1.1611</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8832</v>
+        <v>-1.6967</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1493</v>
+        <v>0.5355</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6461</v>
+        <v>-0.1124</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.198</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1876</v>
+        <v>-0.2382</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5303</v>
+        <v>0.0156</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6572</v>
+        <v>-0.2538</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3214</v>
+        <v>0.9805</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2795</v>
+        <v>0.13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2979</v>
+        <v>0.2888</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0184</v>
+        <v>-0.1588</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0631</v>
+        <v>-0.0493</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7375</v>
+        <v>-0.7272</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6744</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.669</v>
+        <v>0.6675</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7321</v>
+        <v>-0.7168</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.8419</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3297</v>
+        <v>-0.33</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3524</v>
+        <v>-0.5119</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>A. UBAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.2313</v>
+        <v>-2.4778</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0197</v>
+        <v>-3.2645</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2117</v>
+        <v>0.7867</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6301</v>
+        <v>-0.8867</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6248</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0053</v>
+        <v>0.018</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1497</v>
+        <v>-1.1191</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0377</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.112</v>
+        <v>-0.3877</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7798</v>
+        <v>0.2324</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6626</v>
+        <v>-0.1733</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1172</v>
+        <v>0.4057</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.189</v>
+        <v>-1.1765</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9648</v>
+        <v>-0.3651</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1538</v>
+        <v>-0.8115</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1853</v>
+        <v>1.6342</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. UBAL</t>
+          <t>M. STEINBERGS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.682</v>
+        <v>-3.3617</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8118</v>
+        <v>-2.0042</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1297</v>
+        <v>-1.3575</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8887</v>
+        <v>-2.061</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.5292</v>
       </c>
       <c r="I19" t="n">
-        <v>0.016</v>
+        <v>-1.5318</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0926</v>
+        <v>-0.9445</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.714</v>
+        <v>-0.1691</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3786</v>
+        <v>-0.7754</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2038</v>
+        <v>-1.1164</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1908</v>
+        <v>-0.3601</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3946</v>
+        <v>-0.7563</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4025</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.3908</v>
+        <v>-1.6958</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9557</v>
+        <v>-0.832</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4351</v>
+        <v>-0.8637</v>
       </c>
       <c r="V19" t="n">
-        <v>1.639</v>
+        <v>-1.1984</v>
       </c>
       <c r="W19" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>D. PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8136</v>
+        <v>-3.5074</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2489</v>
+        <v>-2.8558</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5647</v>
+        <v>-0.6516</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2993</v>
+        <v>-1.3715</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5612</v>
+        <v>-1.0081</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8605</v>
+        <v>-0.3634</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.045</v>
+        <v>-1.4456</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8934</v>
+        <v>-1.2518</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9383</v>
+        <v>-0.1939</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2543</v>
+        <v>0.0741</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3321</v>
+        <v>0.2437</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9222</v>
+        <v>-0.1695</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7265</v>
+        <v>-0.8188</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0302</v>
+        <v>-0.272</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6962</v>
+        <v>-0.5468</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2019</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0052</v>
+        <v>-3.6945</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.9381</v>
+        <v>-0.9798</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9329</v>
+        <v>-2.7147</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.8584</v>
+        <v>-0.6246</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.7386</v>
+        <v>-0.6233</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1198</v>
+        <v>-0.0013</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.9855</v>
+        <v>0.1355</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.0601</v>
+        <v>0.0237</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0746</v>
+        <v>0.1117</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8729</v>
+        <v>-0.7601</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6785</v>
+        <v>-0.6471</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1945</v>
+        <v>-0.113</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0541</v>
+        <v>-0.6633</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1815</v>
+        <v>0.0229</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2356</v>
+        <v>-0.6862</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. PEREZ</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2088</v>
+        <v>-4.1476</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1932</v>
+        <v>-2.5175</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0156</v>
+        <v>-1.6301</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3738</v>
+        <v>-1.295</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0086</v>
+        <v>0.5656</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3652</v>
+        <v>-1.8605</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.433</v>
+        <v>-0.0639</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2437</v>
+        <v>0.8823</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1893</v>
+        <v>-0.9463</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0592</v>
+        <v>-1.231</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2351</v>
+        <v>-0.3168</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1759</v>
+        <v>-0.9143</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5155</v>
+        <v>-1.0592</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6261</v>
+        <v>-0.2652</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8895</v>
+        <v>-0.794</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-0.8829</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. STEINBERGS</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4385</v>
+        <v>-4.2623</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4505</v>
+        <v>-5.1982</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.988</v>
+        <v>0.9359</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0649</v>
+        <v>-4.851</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-4.7444</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5221</v>
+        <v>-0.1067</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9201</v>
+        <v>-4.0084</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.163</v>
+        <v>-4.0829</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7572</v>
+        <v>0.0745</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1447</v>
+        <v>-0.8426</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3798</v>
+        <v>-0.6615</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7649</v>
+        <v>-0.1811</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.7595</v>
+        <v>-0.3218</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3035</v>
+        <v>-0.0517</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.456</v>
+        <v>-0.2702</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2019</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1855</v>
+        <v>-5.7102</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.6639</v>
+        <v>-6.7202</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4784</v>
+        <v>1.01</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.7443</v>
+        <v>-2.7516</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1933</v>
+        <v>-0.1952</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.551</v>
+        <v>-2.5564</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8472</v>
+        <v>-1.8785</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6098</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.4737</v>
+        <v>-2.4883</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8971</v>
+        <v>-0.8731</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0921</v>
+        <v>-0.5914</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5353</v>
+        <v>-0.5347</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5568</v>
+        <v>-0.0567</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3729</v>
+        <v>0.3643</v>
       </c>
       <c r="W24" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1573</v>
+        <v>-6.458</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.4128</v>
+        <v>-4.6293</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7445</v>
+        <v>-1.8286</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.0538</v>
+        <v>-6.0587</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.3851</v>
+        <v>-4.3856</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.6687</v>
+        <v>-1.673</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.5446</v>
+        <v>-3.579</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.014</v>
+        <v>-3.0347</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5306</v>
+        <v>-0.5443</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.5092</v>
+        <v>-2.4797</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3711</v>
+        <v>-1.351</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7409</v>
+        <v>-1.0431</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5999</v>
+        <v>-0.774</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.141</v>
+        <v>-0.2691</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.27</v>
+        <v>-0.2667</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.3627</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-33.5557</v>
+        <v>-31.1797</v>
       </c>
       <c r="E26" t="n">
-        <v>-28.4724</v>
+        <v>-28.7818</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.0835</v>
+        <v>-2.397900000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-20.8647</v>
+        <v>-20.8099</v>
       </c>
       <c r="H26" t="n">
-        <v>-15.2671</v>
+        <v>-15.2242</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.5976</v>
+        <v>-5.5856</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.149</v>
+        <v>-12.3691</v>
       </c>
       <c r="K26" t="n">
-        <v>-8.4031</v>
+        <v>-8.537200000000002</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.7458</v>
+        <v>-3.8323</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.7157</v>
+        <v>-8.4406</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.864100000000001</v>
+        <v>-6.6873</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.8516</v>
+        <v>-1.7532</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>5.551115123125783e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>-18.1468</v>
+        <v>-18.2107</v>
       </c>
       <c r="R26" t="n">
-        <v>18.1466</v>
+        <v>18.2105</v>
       </c>
       <c r="S26" t="n">
-        <v>-11.8557</v>
+        <v>-9.5244</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.2189</v>
+        <v>-4.209</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.6368</v>
+        <v>-5.3155</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.8353999999999996</v>
+        <v>-0.8454999999999993</v>
       </c>
       <c r="W26" t="n">
-        <v>6.0421</v>
+        <v>6.007000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.8775</v>
+        <v>-6.8522</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104636_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104636_W20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>1.5479</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.096299999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104636_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-6.8522</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
